--- a/data/mapping_files/cell_type_mappings_2.xlsx
+++ b/data/mapping_files/cell_type_mappings_2.xlsx
@@ -67,7 +67,7 @@
     <t>acinar cell</t>
   </si>
   <si>
-    <t>oralcavity-codex-czi</t>
+    <t>mouth-codex-czi</t>
   </si>
   <si>
     <t>UBERON:0000167</t>
